--- a/0176_Cuenca_Coata/_raw_reportes_xlsx/IDConfig_67614_completo.xlsx
+++ b/0176_Cuenca_Coata/_raw_reportes_xlsx/IDConfig_67614_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rea56eae10f544aba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R677a787020d849c0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.0887</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.0887</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.0887</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +399,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.5936</x:v>
+        <x:v>      7.0609</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -279,7 +414,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.4618</x:v>
+        <x:v>      7.8618</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -294,7 +429,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.1138</x:v>
+        <x:v>      8.4317</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -309,7 +444,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.1138</x:v>
+        <x:v>      8.4317</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -324,7 +459,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.1138</x:v>
+        <x:v>      8.4317</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -339,7 +474,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.1138</x:v>
+        <x:v>      8.4317</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -354,7 +489,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.1138</x:v>
+        <x:v>      8.4317</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -369,7 +504,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.1138</x:v>
+        <x:v>      8.4317</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -384,7 +519,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.4618</x:v>
+        <x:v>      7.8618</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -399,7 +534,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.7801</x:v>
+        <x:v>      8.1430</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -414,7 +549,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.4618</x:v>
+        <x:v>      7.8618</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -429,7 +564,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.4618</x:v>
+        <x:v>      7.8618</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -444,7 +579,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.4618</x:v>
+        <x:v>      7.8618</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -459,7 +594,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.1138</x:v>
+        <x:v>      8.4317</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -474,7 +609,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.1138</x:v>
+        <x:v>      8.4317</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -489,7 +624,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.4635</x:v>
+        <x:v>      8.7278</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -504,7 +639,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.4618</x:v>
+        <x:v>      7.8618</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -519,7 +654,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.4618</x:v>
+        <x:v>      7.8618</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -534,7 +669,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -549,7 +684,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -564,7 +699,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -579,7 +714,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -594,7 +729,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -609,7 +744,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -624,7 +759,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -639,7 +774,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -654,7 +789,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.4635</x:v>
+        <x:v>      8.7278</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -669,7 +804,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.4635</x:v>
+        <x:v>      8.7278</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -684,7 +819,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.4635</x:v>
+        <x:v>      8.7278</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -699,7 +834,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.4635</x:v>
+        <x:v>      8.7278</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -714,7 +849,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.4635</x:v>
+        <x:v>      8.7278</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -729,7 +864,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.4635</x:v>
+        <x:v>      8.7278</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -744,7 +879,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -759,7 +894,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -774,7 +909,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -789,7 +924,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.2132</x:v>
+        <x:v>      9.3429</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -804,7 +939,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.2132</x:v>
+        <x:v>      9.3429</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -819,7 +954,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -834,7 +969,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.2132</x:v>
+        <x:v>      9.3429</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -849,7 +984,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -864,7 +999,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -879,7 +1014,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -894,7 +1029,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -909,7 +1044,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -924,7 +1059,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -939,7 +1074,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.2132</x:v>
+        <x:v>      9.3429</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -954,7 +1089,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -969,7 +1104,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -984,7 +1119,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -999,7 +1134,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1014,7 +1149,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1029,7 +1164,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8298</x:v>
+        <x:v>      9.0315</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1044,7 +1179,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1059,7 +1194,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1074,7 +1209,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1089,7 +1224,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1104,7 +1239,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1119,7 +1254,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.0345</x:v>
+        <x:v>      9.9894</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1134,7 +1269,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1149,7 +1284,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1164,7 +1299,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1179,7 +1314,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1194,7 +1329,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1209,7 +1344,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1224,7 +1359,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.0345</x:v>
+        <x:v>      9.9894</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1239,7 +1374,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.9132</x:v>
+        <x:v>     11.3808</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1254,7 +1389,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.9326</x:v>
+        <x:v>     10.6684</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1269,7 +1404,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6146</x:v>
+        <x:v>      9.6622</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1284,7 +1419,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.0345</x:v>
+        <x:v>      9.9894</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1299,7 +1434,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.4735</x:v>
+        <x:v>     10.3248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1314,7 +1449,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.4735</x:v>
+        <x:v>     10.3248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1329,7 +1464,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.4735</x:v>
+        <x:v>     10.3248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1344,7 +1479,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.9132</x:v>
+        <x:v>     11.3808</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1359,7 +1494,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.4364</x:v>
+        <x:v>     11.7499</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1374,7 +1509,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9825</x:v>
+        <x:v>     12.1278</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1389,7 +1524,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5523</x:v>
+        <x:v>     12.5145</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1404,7 +1539,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.1466</x:v>
+        <x:v>     12.9103</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1419,7 +1554,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.4124</x:v>
+        <x:v>     13.7294</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1434,7 +1569,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     15.5169</x:v>
+        <x:v>     15.0291</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1449,7 +1584,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     17.0682</x:v>
+        <x:v>     15.9446</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1464,7 +1599,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     15.5169</x:v>
+        <x:v>     15.0291</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1479,7 +1614,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.4122</x:v>
+        <x:v>     11.0204</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1494,7 +1629,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.4735</x:v>
+        <x:v>     10.3248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1509,7 +1644,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.4735</x:v>
+        <x:v>     10.3248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1524,7 +1659,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.4735</x:v>
+        <x:v>     10.3248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1539,7 +1674,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.4735</x:v>
+        <x:v>     10.3248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1554,7 +1689,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.4735</x:v>
+        <x:v>     10.3248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1569,7 +1704,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.9326</x:v>
+        <x:v>     10.6684</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1584,7 +1719,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.4122</x:v>
+        <x:v>     11.0204</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1599,7 +1734,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.4122</x:v>
+        <x:v>     11.0204</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1614,7 +1749,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.4122</x:v>
+        <x:v>     11.0204</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1629,7 +1764,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5523</x:v>
+        <x:v>     12.5145</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1644,7 +1779,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.1466</x:v>
+        <x:v>     12.9103</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1659,7 +1794,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.7664</x:v>
+        <x:v>     13.3152</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1674,7 +1809,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     14.0855</x:v>
+        <x:v>     14.1530</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1689,7 +1824,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     15.5169</x:v>
+        <x:v>     15.0291</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1704,7 +1839,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     16.2771</x:v>
+        <x:v>     15.4819</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1719,7 +1854,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     20.5624</x:v>
+        <x:v>     17.8983</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1734,7 +1869,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     30.6602</x:v>
+        <x:v>     22.9341</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1749,7 +1884,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     23.5597</x:v>
+        <x:v>     19.4753</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1764,7 +1899,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     27.3397</x:v>
+        <x:v>     26.1461</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1779,7 +1914,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     30.6602</x:v>
+        <x:v>     24.8240</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1794,7 +1929,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     26.1464</x:v>
+        <x:v>     24.8240</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1809,7 +1944,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     25.5620</x:v>
+        <x:v>     24.1817</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1824,7 +1959,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     26.7390</x:v>
+        <x:v>     25.4787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1839,7 +1974,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     27.9486</x:v>
+        <x:v>     26.8263</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1854,7 +1989,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     28.5655</x:v>
+        <x:v>     27.5195</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1869,7 +2004,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     31.1145</x:v>
+        <x:v>     30.6599</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1884,7 +2019,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     34.4835</x:v>
+        <x:v>     35.3030</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1899,7 +2034,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.7935</x:v>
+        <x:v>     34.3656</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1914,7 +2049,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.1817</x:v>
+        <x:v>     36.2448</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1929,7 +2064,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     41.0594</x:v>
+        <x:v>     43.9371</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1944,7 +2079,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     48.2931</x:v>
+        <x:v>     52.9268</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1959,7 +2094,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.1931</x:v>
+        <x:v>     47.8886</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1974,7 +2109,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.8880</x:v>
+        <x:v>     37.1910</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1989,7 +2124,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     36.6024</x:v>
+        <x:v>     38.1415</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2004,7 +2139,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.7935</x:v>
+        <x:v>     34.3656</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2019,7 +2154,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.1817</x:v>
+        <x:v>     36.2448</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2034,7 +2169,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     39.5412</x:v>
+        <x:v>     41.9877</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2049,7 +2184,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     42.6100</x:v>
+        <x:v>     45.9041</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2064,7 +2199,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.6288</x:v>
+        <x:v>     50.8984</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2079,7 +2214,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     50.8505</x:v>
+        <x:v>     56.0024</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2094,7 +2229,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     63.7516</x:v>
+        <x:v>     70.8775</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2109,7 +2244,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     69.7680</x:v>
+        <x:v>     77.5160</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2124,7 +2259,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     63.7516</x:v>
+        <x:v>     70.8775</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2139,7 +2274,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     69.7680</x:v>
+        <x:v>     77.5160</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2154,7 +2289,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     89.5713</x:v>
+        <x:v>     98.3796</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2169,7 +2304,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     80.4450</x:v>
+        <x:v>     88.9313</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2184,7 +2319,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     80.4450</x:v>
+        <x:v>     88.9313</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2199,7 +2334,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     88.4021</x:v>
+        <x:v>     97.1832</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2214,7 +2349,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     94.3294</x:v>
+        <x:v>    103.2091</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2229,7 +2364,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     80.4450</x:v>
+        <x:v>     88.9313</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2244,7 +2379,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     91.9341</x:v>
+        <x:v>    100.7856</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2259,7 +2394,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    124.2102</x:v>
+        <x:v>    132.3420</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2274,7 +2409,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    155.2448</x:v>
+        <x:v>    160.9697</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2289,7 +2424,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    137.0722</x:v>
+        <x:v>    144.3739</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2304,7 +2439,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    171.2820</x:v>
+        <x:v>    175.2824</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2319,7 +2454,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    161.5622</x:v>
+        <x:v>    166.6421</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2334,7 +2469,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    177.9243</x:v>
+        <x:v>    181.1304</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2349,7 +2484,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    177.9243</x:v>
+        <x:v>    181.1304</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2364,7 +2499,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    134.1571</x:v>
+        <x:v>    141.6694</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2379,7 +2514,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    106.7931</x:v>
+        <x:v>    115.5902</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2394,7 +2529,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    118.7049</x:v>
+        <x:v>    127.1086</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2409,7 +2544,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    112.0060</x:v>
+        <x:v>    120.6656</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2424,7 +2559,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     79.3407</x:v>
+        <x:v>     87.7700</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2439,7 +2574,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     47.4569</x:v>
+        <x:v>     51.9104</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2454,7 +2589,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     50.8505</x:v>
+        <x:v>     56.0024</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2469,7 +2604,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     54.3741</x:v>
+        <x:v>     60.1646</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2484,7 +2619,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     53.4810</x:v>
+        <x:v>     59.1175</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2499,7 +2634,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     63.7516</x:v>
+        <x:v>     70.8775</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2514,7 +2649,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     75.0050</x:v>
+        <x:v>     83.1688</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2529,7 +2664,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     89.5713</x:v>
+        <x:v>     98.3796</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2544,7 +2679,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    109.3833</x:v>
+        <x:v>    118.1191</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2559,7 +2694,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    158.3873</x:v>
+        <x:v>    163.7971</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2574,7 +2709,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    156.8120</x:v>
+        <x:v>    162.3812</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2589,7 +2724,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    127.0115</x:v>
+        <x:v>    134.9850</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2604,7 +2739,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     83.8064</x:v>
+        <x:v>     92.4415</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2619,7 +2754,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     43.3975</x:v>
+        <x:v>     46.8942</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2634,7 +2769,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     34.4835</x:v>
+        <x:v>     35.3030</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2649,7 +2784,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     42.6100</x:v>
+        <x:v>     45.9041</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2664,7 +2799,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     28.5655</x:v>
+        <x:v>     27.5195</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2679,7 +2814,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     20.5624</x:v>
+        <x:v>     17.8983</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2694,7 +2829,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     22.5225</x:v>
+        <x:v>     18.9387</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2709,7 +2844,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     28.1178</x:v>
+        <x:v>     21.7346</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2724,7 +2859,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     31.1145</x:v>
+        <x:v>     30.6599</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2739,7 +2874,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     26.1464</x:v>
+        <x:v>     24.8240</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2754,7 +2889,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     27.9486</x:v>
+        <x:v>     26.8263</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2769,7 +2904,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     28.5655</x:v>
+        <x:v>     27.5195</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2784,7 +2919,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     32.4377</x:v>
+        <x:v>     32.5040</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2799,7 +2934,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     36.6024</x:v>
+        <x:v>     38.1415</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2814,7 +2949,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     41.0594</x:v>
+        <x:v>     43.9371</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2829,7 +2964,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     44.9969</x:v>
+        <x:v>     48.8875</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2844,7 +2979,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     53.4810</x:v>
+        <x:v>     59.1175</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2859,7 +2994,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     41.0594</x:v>
+        <x:v>     43.9371</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2874,7 +3009,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     43.3975</x:v>
+        <x:v>     46.8942</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2889,7 +3024,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     47.4569</x:v>
+        <x:v>     51.9104</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2904,7 +3039,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     58.0277</x:v>
+        <x:v>     64.3971</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2919,7 +3054,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     72.8858</x:v>
+        <x:v>     80.8945</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2934,7 +3069,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     91.9341</x:v>
+        <x:v>    100.7856</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2949,7 +3084,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    110.6906</x:v>
+        <x:v>    119.3902</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2964,7 +3099,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     49.1374</x:v>
+        <x:v>     53.9476</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2979,7 +3114,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     48.2931</x:v>
+        <x:v>     52.9268</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2994,7 +3129,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     46.6288</x:v>
+        <x:v>     50.8984</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3009,7 +3144,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     55.2753</x:v>
+        <x:v>     61.2162</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3024,7 +3159,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     67.7301</x:v>
+        <x:v>     75.2856</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3039,7 +3174,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     69.7680</x:v>
+        <x:v>     77.5160</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3054,7 +3189,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     96.7572</x:v>
+        <x:v>    105.6502</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3069,7 +3204,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    127.0115</x:v>
+        <x:v>    134.9850</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3084,7 +3219,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     99.2174</x:v>
+        <x:v>    108.1089</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3099,7 +3234,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    125.6068</x:v>
+        <x:v>    133.6613</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3114,7 +3249,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    159.9707</x:v>
+        <x:v>    165.2174</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3129,7 +3264,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    131.2745</x:v>
+        <x:v>    138.9825</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3144,7 +3279,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    179.6052</x:v>
+        <x:v>    182.6034</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3159,7 +3294,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    209.4227</x:v>
+        <x:v>    208.3156</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3174,7 +3309,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    239.6304</x:v>
+        <x:v>    233.6743</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3189,7 +3324,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    134.1571</x:v>
+        <x:v>    141.6694</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3204,7 +3339,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    195.0986</x:v>
+        <x:v>    196.0577</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3219,7 +3354,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    122.8217</x:v>
+        <x:v>    131.0270</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3234,7 +3369,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    129.8454</x:v>
+        <x:v>    137.6456</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3249,7 +3384,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    137.0722</x:v>
+        <x:v>    144.3739</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3264,7 +3399,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    156.8120</x:v>
+        <x:v>    162.3812</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3279,7 +3414,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    209.4227</x:v>
+        <x:v>    208.3156</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3294,7 +3429,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    146.0123</x:v>
+        <x:v>    152.5928</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3309,7 +3444,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    117.3489</x:v>
+        <x:v>    125.8112</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3324,7 +3459,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    195.0986</x:v>
+        <x:v>    196.0577</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3339,7 +3474,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    211.2498</x:v>
+        <x:v>    209.8676</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3354,7 +3489,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    112.0060</x:v>
+        <x:v>    120.6656</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3369,7 +3504,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    121.4413</x:v>
+        <x:v>    129.7165</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3384,7 +3519,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    129.8454</x:v>
+        <x:v>    137.6456</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3399,7 +3534,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     69.7680</x:v>
+        <x:v>     77.5160</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3414,7 +3549,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     73.9413</x:v>
+        <x:v>     82.0294</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3429,7 +3564,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     47.4569</x:v>
+        <x:v>     51.9104</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3444,7 +3579,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     22.5225</x:v>
+        <x:v>     18.9387</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3459,7 +3594,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     17.8912</x:v>
+        <x:v>     16.4175</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3474,7 +3609,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     15.5169</x:v>
+        <x:v>     15.0291</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3489,7 +3624,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     17.8912</x:v>
+        <x:v>     16.4175</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3504,7 +3639,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     23.5597</x:v>
+        <x:v>     19.4753</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3519,7 +3654,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     26.9144</x:v>
+        <x:v>     21.1526</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3534,7 +3669,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     28.5655</x:v>
+        <x:v>     27.5195</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3549,7 +3684,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.1817</x:v>
+        <x:v>     36.2448</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3564,7 +3699,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     41.8306</x:v>
+        <x:v>     44.9184</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3579,7 +3714,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     33.1115</x:v>
+        <x:v>     33.4326</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3594,7 +3729,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     30.6602</x:v>
+        <x:v>     22.9341</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3609,7 +3744,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     30.6602</x:v>
+        <x:v>     22.9341</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3624,7 +3759,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     30.6602</x:v>
+        <x:v>     24.8240</x:v>
       </x:c>
     </x:row>
     <x:row>

--- a/0176_Cuenca_Coata/_raw_reportes_xlsx/IDConfig_67614_completo.xlsx
+++ b/0176_Cuenca_Coata/_raw_reportes_xlsx/IDConfig_67614_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R677a787020d849c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R9f68c50153a84c65"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.0887</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.0887</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.0887</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5615</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.0609</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.0609</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.3208</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.3208</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.3208</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8618</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.1430</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.7278</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.5877</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.5877</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.1430</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.0609</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.0609</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.0609</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.5877</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.3208</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.3208</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.0609</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.0609</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5615</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5615</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5615</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5615</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5615</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5615</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
